--- a/daily_output/Shopee_upload_SG_2026-09-30.xlsx
+++ b/daily_output/Shopee_upload_SG_2026-09-30.xlsx
@@ -12878,7 +12878,7 @@
     <t xml:space="preserve">B0F5B4Z93Y</t>
   </si>
   <si>
-    <t xml:space="preserve">https://m.media-amazon.com/images/I/61r3PWqPWJL._AC_SL1000_.jpg</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/jyankel0726switch-code/ai-management-shopee/claude/admiring-bardeen-8xil2p/framed-images/B0F5B4Z93Y_cover.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">https://m.media-amazon.com/images/I/51Ey6MLwoHL._AC_SL1000_.jpg</t>
@@ -12924,7 +12924,7 @@
     <t xml:space="preserve">B0G2LSVHPZ</t>
   </si>
   <si>
-    <t xml:space="preserve">https://m.media-amazon.com/images/I/61j90k+VV9L._AC_SL1000_.jpg</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/jyankel0726switch-code/ai-management-shopee/claude/admiring-bardeen-8xil2p/framed-images/B0G2LSVHPZ_cover.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">https://m.media-amazon.com/images/I/51LHA8P2IjL.jpg</t>
@@ -12967,7 +12967,7 @@
     <t xml:space="preserve">B0DSBRLTC9</t>
   </si>
   <si>
-    <t xml:space="preserve">https://m.media-amazon.com/images/I/61sF2VfgeuL._AC_SL1089_.jpg</t>
+    <t xml:space="preserve">https://raw.githubusercontent.com/jyankel0726switch-code/ai-management-shopee/claude/admiring-bardeen-8xil2p/framed-images/B0DSBRLTC9_cover.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">https://m.media-amazon.com/images/I/61LnoKuPWRL._AC_SL1000_.jpg</t>
